--- a/dim_wishlists/spreadsheets_to_dim_wishlists/workbooks_downloaded/aegis_endgame_exotic_weapons.xlsx
+++ b/dim_wishlists/spreadsheets_to_dim_wishlists/workbooks_downloaded/aegis_endgame_exotic_weapons.xlsx
@@ -1838,3843 +1838,3843 @@
     <xdr:ext cx="476250" cy="476250"/>
     <xdr:pic>
       <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image97.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image9.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image28.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image17.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image13.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image8.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image72.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image7.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image14.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image55.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image11.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image10.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image23.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image45.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image30.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image16.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image31.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image112.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image41.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image60.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image26.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image21.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image107.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image29.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image39.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image46.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image50.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image18.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image12.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image19.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image43.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image20.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image33.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image119.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image71.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image84.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image24.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image53.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image129.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image15.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image136.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image76.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image27.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image56.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image25.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image58.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image22.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image130.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image34.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image36.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image132.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image64.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image32.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image69.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image47.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image91.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image57.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image42.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image48.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image80.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image37.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image35.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image122.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image44.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image38.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image61.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image54.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image40.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image124.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image49.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image51.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image88.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image67.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image52.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image65.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image63.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image85.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image138.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image87.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image68.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image79.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image128.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image70.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image131.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId90"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image135.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId91"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image75.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image66.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image74.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image62.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image59.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image125.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId97"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image104.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId98"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image73.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId99"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image100.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId100"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image83.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId101"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image127.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId102"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image82.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId103"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image121.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image77.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId105"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image109.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId106"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image93.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId107"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image78.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image103.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image101.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId110"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image110.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId111"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image81.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId112"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image89.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId113"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image123.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId114"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image96.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId115"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image86.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId116"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image94.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId117"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image117.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId118"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image95.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId119"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image118.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId120"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image116.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId121"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image134.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId122"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>124</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image114.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId123"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image137.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId124"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image90.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId125"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image120.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId126"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image105.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId127"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image106.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId128"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image92.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId129"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image111.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId130"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image113.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId131"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image102.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId132"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
         <xdr:cNvPr id="0" name="image108.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image25.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image20.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image10.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image12.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image40.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image29.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image14.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image8.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image33.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image41.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image11.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image9.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image121.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image32.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image22.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image21.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image107.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image54.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image46.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image19.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image38.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image13.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image44.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image62.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image15.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image72.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image128.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image27.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image49.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image24.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image50.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image111.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image16.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image18.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image31.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
+        <a:blip cstate="print" r:embed="rId133"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image98.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId134"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image126.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId135"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image99.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId136"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image115.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId137"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="476250" cy="476250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="0" name="image133.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image137.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId45"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image23.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId46"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image64.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId47"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image60.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId48"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image17.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId49"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image45.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId50"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image30.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId51"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image61.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId52"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image28.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId53"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image123.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId54"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image34.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId55"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image36.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId56"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image122.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId57"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image35.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId58"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image26.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId59"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image78.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId60"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image37.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId61"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image39.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId62"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image77.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId63"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image55.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId64"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image132.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId65"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image69.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId66"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image53.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId67"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image47.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId68"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image124.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId69"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image63.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId70"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image52.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId71"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image59.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId72"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image42.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId73"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image43.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId74"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image126.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId75"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image110.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId76"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image67.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId77"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image74.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId78"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image48.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId79"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image51.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId80"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image57.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId81"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image66.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId82"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image101.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId83"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image73.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId84"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image85.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId85"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image56.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId86"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image58.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId87"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image84.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId88"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image65.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId89"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image129.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId90"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image103.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId91"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image70.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId92"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image68.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId93"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image71.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId94"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image130.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId95"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image131.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId96"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image119.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId97"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image76.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId98"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image75.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId99"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image96.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId100"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image134.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId101"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image80.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId102"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image82.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId103"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image127.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId104"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image86.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId105"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image90.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId106"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image98.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId107"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image94.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId108"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image104.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId109"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image83.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId110"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image138.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId111"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image87.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId112"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image92.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId113"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image125.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId114"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image105.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId115"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image81.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId116"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image136.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId117"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image115.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId118"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image89.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId119"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image113.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId120"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image97.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId121"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image91.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId122"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>124</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image114.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId123"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image95.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId124"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image79.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId125"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image88.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId126"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>128</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image93.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId127"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image116.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId128"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image99.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId129"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>131</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image118.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId130"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>132</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image120.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId131"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>133</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image102.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId132"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>134</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image100.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId133"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>135</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image106.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId134"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image117.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId135"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image109.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId136"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image112.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId137"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image135.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>

--- a/dim_wishlists/spreadsheets_to_dim_wishlists/workbooks_downloaded/aegis_endgame_exotic_weapons.xlsx
+++ b/dim_wishlists/spreadsheets_to_dim_wishlists/workbooks_downloaded/aegis_endgame_exotic_weapons.xlsx
@@ -1838,57 +1838,1513 @@
     <xdr:ext cx="476250" cy="476250"/>
     <xdr:pic>
       <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image127.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image15.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image24.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image44.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image42.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image5.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image2.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image56.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image7.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image1.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image115.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image20.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image26.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image8.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image31.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image61.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image18.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image3.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image12.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image23.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image4.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image135.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image88.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image33.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image29.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image13.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image48.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image14.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image75.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image60.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image53.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image10.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image39.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image9.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image100.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image131.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image78.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image6.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image30.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image110.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image71.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image11.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image27.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image129.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image17.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image62.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image47.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image52.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image16.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image37.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image21.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image46.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image25.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
         <xdr:cNvPr id="0" name="image97.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image9.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="476250" cy="476250"/>
@@ -1898,137 +3354,473 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image17.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image13.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image8.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>9</xdr:row>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image22.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image106.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image50.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image19.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image66.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image32.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image77.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image57.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image40.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId64"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image80.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image89.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image35.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image55.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image111.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image51.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId70"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image34.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId71"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="476250" cy="476250"/>
@@ -2038,221 +3830,109 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image14.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image55.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image11.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image10.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId14"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image23.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+        <a:blip cstate="print" r:embed="rId72"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image41.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId73"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image132.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId74"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image123.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId75"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="476250" cy="476250"/>
@@ -2262,193 +3942,1257 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId16"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId18"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image30.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image16.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image31.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
+        <a:blip cstate="print" r:embed="rId76"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image43.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId77"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image64.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId78"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image36.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId79"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image38.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId80"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image108.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId81"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image49.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId82"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image73.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId83"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image69.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId84"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image68.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId85"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image82.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId86"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>88</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image54.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId87"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image81.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId88"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image58.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId89"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image137.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId90"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image90.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId91"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image59.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId92"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image136.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId93"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>95</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image63.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image65.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>97</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image103.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image128.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId97"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image70.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId98"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>100</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image94.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId99"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image87.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId100"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image76.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId101"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image67.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId102"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image96.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId103"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>105</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image126.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>106</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image83.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId105"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image102.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId106"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image134.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId107"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>109</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image84.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image109.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image79.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId110"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>112</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image105.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId111"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>113</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image74.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId112"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>114</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image125.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId113"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>115</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image121.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId114"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image107.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId115"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>117</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image133.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId116"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>118</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image85.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId117"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image104.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId118"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>120</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image86.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId119"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image124.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId120"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="476250" cy="476250"/>
@@ -2458,473 +5202,53 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image41.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image60.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId25"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image26.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image21.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image107.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image29.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image39.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image46.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image50.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image18.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image12.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image19.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image43.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image20.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image33.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId39"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+        <a:blip cstate="print" r:embed="rId121"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image120.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId122"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="476250" cy="476250"/>
@@ -2934,389 +5258,193 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId40"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image71.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image84.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image24.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image53.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image129.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId45"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image15.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId46"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image136.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId47"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image76.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId48"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image27.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId49"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image56.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId50"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image25.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId51"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image58.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId52"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image22.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId53"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>55</xdr:row>
+        <a:blip cstate="print" r:embed="rId123"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>125</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image122.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId124"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image93.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId125"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image92.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId126"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image116.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId127"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>129</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image113.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId128"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>130</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image101.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId129"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="476250" cy="476250"/>
@@ -3326,221 +5454,81 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId54"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image34.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId55"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image36.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId56"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image132.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId57"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image64.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId58"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image32.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId59"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image69.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId60"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image47.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId61"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+        <a:blip cstate="print" r:embed="rId130"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>132</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image114.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId131"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image99.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId132"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="476250" cy="476250"/>
@@ -3550,2131 +5538,143 @@
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId62"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image57.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId63"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image42.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId64"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image48.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId65"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image80.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId66"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image37.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId67"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image35.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId68"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image122.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId69"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image44.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId70"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image38.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId71"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image61.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId72"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>74</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image54.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId73"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>75</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image40.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId74"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image124.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId75"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image49.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId76"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image51.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId77"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image88.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId78"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image67.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId79"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image52.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId80"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image65.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId81"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image63.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId82"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image85.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId83"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
+        <a:blip cstate="print" r:embed="rId133"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>135</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image95.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId134"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image117.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId135"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>137</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image98.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId136"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>138</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="476250" cy="476250"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="image118.jpg"/>
+        <xdr:cNvPicPr preferRelativeResize="0"/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip cstate="print" r:embed="rId137"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="476250" cy="476250"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="0" name="image138.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId84"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image87.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId85"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image68.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId86"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image79.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId87"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image128.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId88"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image70.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId89"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image131.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId90"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image135.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId91"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image75.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId92"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image66.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId93"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image74.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId94"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image62.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId95"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image59.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId96"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image125.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId97"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image104.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId98"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image73.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId99"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image100.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId100"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image83.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId101"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image127.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId102"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>104</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image82.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId103"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image121.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId104"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image77.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId105"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>107</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image109.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId106"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image93.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId107"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image78.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId108"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image103.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId109"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image101.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId110"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image110.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId111"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image81.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId112"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image89.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId113"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image123.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId114"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image96.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId115"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image86.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId116"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image94.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId117"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>119</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image117.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId118"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image95.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId119"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image118.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId120"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>122</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image116.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId121"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image134.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId122"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>124</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image114.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId123"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image137.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId124"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>126</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image90.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId125"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image120.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId126"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>128</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image105.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId127"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>129</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image106.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId128"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>130</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image92.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId129"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>131</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image111.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId130"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>132</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image113.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId131"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>133</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image102.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId132"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>134</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image108.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId133"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>135</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image98.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId134"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>136</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image126.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId135"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image99.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId136"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>138</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image115.jpg"/>
-        <xdr:cNvPicPr preferRelativeResize="0"/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId137"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="476250" cy="476250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image133.jpg"/>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
